--- a/results.xlsx
+++ b/results.xlsx
@@ -425,26 +425,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="32" customWidth="1" min="19" max="19"/>
     <col width="35" customWidth="1" min="20" max="20"/>
@@ -561,12 +561,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>PEO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>PEO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -576,53 +576,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jordi Gel DVB 500 RP</t>
+          <t>LUNA C18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jordi</t>
+          <t>Phenomenex</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reversed phase (polymeric)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>divinylbenzene</t>
-        </is>
-      </c>
+          <t>reversed phase</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>250x4.6 mm</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>500 A</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>5 um</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Acetone / Water</t>
-        </is>
-      </c>
+          <t>250 x 4.6 mm</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>92/8</t>
+          <t>60/40</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -635,11 +615,7 @@
           <t>29 °C</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.5 mL/min</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>100 µL</t>
@@ -649,19 +625,19 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>determine the length of PO block(s) at the CAP for EO; separation of EO-PO copolymers by critical conditions</t>
+          <t>separation of block copolymers by microstructure; characterization of diblock copolymer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>PEO-b-PLLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>PEO-b-PLLA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -671,53 +647,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Discovery HS-PEG</t>
+          <t>LUNA C18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Supelco</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>normal phase</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>silica</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PEG</t>
-        </is>
-      </c>
+          <t>reversed phase</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>250x4.6 mm</t>
+          <t>250 x 4.6 mm</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>120 A</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>5 um</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Acetone / Water</t>
+          <t>Acetonitrile / Water</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>92/8</t>
+          <t>60/40</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -730,81 +690,57 @@
           <t>29 °C</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.5 mL/min</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>100 µL</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Separation of poloxamers and identification of PEG presence; determination of molar mass distribution of the individual blocks</t>
+          <t>separation of PEO-b-PLLA by critical conditions</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>poly(ethylene glycol), poly(propylene glycol)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>PEO-b-PLLA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PEO-b-PLLA</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Nucleosil 100-5 OH</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Macherey-Nagel</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>normal phase</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>silica</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Diol</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>250x4.6 mm</t>
-        </is>
-      </c>
+          <t>reversed phase</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>100 A</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>5 um</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Acetone / Water</t>
+          <t>Acetonitrile / Water</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>80/20</t>
+          <t>54/46</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -817,11 +753,7 @@
           <t>29 °C</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0.5 mL/min</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>100 µL</t>
@@ -831,161 +763,7 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>determine the total MMD by SEC, length of EO block(s) at CAP for PO, and length of PO block at CAP for EO; Separation of poloxamers according to the length of PO blocks and identification of PEG presence</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>EO-PO copolymers</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EO-PO copolymers</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>reversed phase</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Acetone / Water</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>92/8</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>vol%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>29 °C</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0.5 mL/min</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>separation of EO-PO copolymers by critical conditions</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EO</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EO</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Jordi Gel DVB 500 RP</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Jordi</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>reversed phase</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>divinylbenzene</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>250x4.6 mm</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>500 A</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>5 um</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Acetone / Water</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>90/10</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>vol%</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>29 °C</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0.5 mL/min</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>determination of critical adsorption point (CAP) for EO</t>
+          <t>separation of PEO-b-PLLA diblock copolymers by microstructure</t>
         </is>
       </c>
     </row>
